--- a/results/canaliculi/543_3/measurements.xlsx
+++ b/results/canaliculi/543_3/measurements.xlsx
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102.7273</v>
+        <v>125.2222</v>
       </c>
       <c r="C6" t="n">
         <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>77.3978</v>
+        <v>86.0055</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157.4599</v>
+        <v>162.866</v>
       </c>
       <c r="C7" t="n">
         <v>132.6852</v>
       </c>
       <c r="D7" t="n">
-        <v>58.0475</v>
+        <v>63.4999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,13 +695,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="C7" t="n">
-        <v>22667.0795</v>
+        <v>48040.9888</v>
       </c>
       <c r="D7" t="n">
-        <v>179.8975</v>
+        <v>222.412</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +717,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>18672.6545</v>
+        <v>10880.1848</v>
       </c>
       <c r="D8" t="n">
-        <v>202.9636</v>
+        <v>132.6852</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -739,13 +739,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>10880.1848</v>
+        <v>9990.4822</v>
       </c>
       <c r="D9" t="n">
-        <v>132.6852</v>
+        <v>135.0065</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +761,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>9990.4822</v>
+        <v>6828.9124</v>
       </c>
       <c r="D10" t="n">
-        <v>135.0065</v>
+        <v>103.4684</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,62 +783,18 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="C11" t="n">
-        <v>2492.1089</v>
+        <v>43922.8679</v>
       </c>
       <c r="D11" t="n">
-        <v>95.8503</v>
+        <v>224.0963</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>41</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4650.7964</v>
-      </c>
-      <c r="D12" t="n">
-        <v>113.4341</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>196</v>
-      </c>
-      <c r="C13" t="n">
-        <v>43922.8679</v>
-      </c>
-      <c r="D13" t="n">
-        <v>224.0963</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>px</t>
         </is>

--- a/results/canaliculi/543_3/measurements.xlsx
+++ b/results/canaliculi/543_3/measurements.xlsx
@@ -433,6 +433,11 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>assignment_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +451,11 @@
       <c r="C2" t="n">
         <v>9</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,13 +503,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.2222</v>
+        <v>73</v>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>86.0055</v>
+        <v>55.6192</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -517,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>162.866</v>
+        <v>133.1805</v>
       </c>
       <c r="C7" t="n">
-        <v>132.6852</v>
+        <v>85.854</v>
       </c>
       <c r="D7" t="n">
-        <v>63.4999</v>
+        <v>97.06319999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>11226.1584</v>
+        <v>2497.8439</v>
       </c>
       <c r="D2" t="n">
-        <v>124.7351</v>
+        <v>67.5093</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -607,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>310</v>
+        <v>137</v>
       </c>
       <c r="C3" t="n">
-        <v>91432.8463</v>
+        <v>22862.8285</v>
       </c>
       <c r="D3" t="n">
-        <v>294.9447</v>
+        <v>166.882</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -629,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="C4" t="n">
-        <v>31323.9498</v>
+        <v>68043.3958</v>
       </c>
       <c r="D4" t="n">
-        <v>203.4023</v>
+        <v>358.1231</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -651,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>7928.8039</v>
+        <v>2170.1921</v>
       </c>
       <c r="D5" t="n">
-        <v>127.8839</v>
+        <v>72.33969999999999</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -673,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>8851.6638</v>
+        <v>3379.1698</v>
       </c>
       <c r="D6" t="n">
-        <v>121.2557</v>
+        <v>78.5853</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -695,13 +705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>48040.9888</v>
+        <v>13349.3942</v>
       </c>
       <c r="D7" t="n">
-        <v>222.412</v>
+        <v>158.9214</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>10880.1848</v>
+        <v>4206.846</v>
       </c>
       <c r="D8" t="n">
-        <v>132.6852</v>
+        <v>85.854</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -739,13 +749,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>9990.4822</v>
+        <v>9978.6142</v>
       </c>
       <c r="D9" t="n">
-        <v>135.0065</v>
+        <v>169.1291</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +771,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>6828.9124</v>
+        <v>1155.862</v>
       </c>
       <c r="D10" t="n">
-        <v>103.4684</v>
+        <v>41.2808</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>196</v>
+        <v>124</v>
       </c>
       <c r="C11" t="n">
-        <v>43922.8679</v>
+        <v>34426.5906</v>
       </c>
       <c r="D11" t="n">
-        <v>224.0963</v>
+        <v>277.6338</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>

--- a/results/canaliculi/543_3/measurements.xlsx
+++ b/results/canaliculi/543_3/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>graph</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>73</v>
-      </c>
-      <c r="C6" t="n">
-        <v>49</v>
-      </c>
-      <c r="D6" t="n">
-        <v>55.6192</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>9</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>23.7778</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18.2536</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>744.2212</v>
+      </c>
+      <c r="C8" t="n">
+        <v>586.7178</v>
+      </c>
+      <c r="D8" t="n">
+        <v>477.3259</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>133.1805</v>
-      </c>
-      <c r="C7" t="n">
-        <v>85.854</v>
-      </c>
-      <c r="D7" t="n">
-        <v>97.06319999999999</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>34.846</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34.7536</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.0534</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>2497.8439</v>
+        <v>526.7006</v>
       </c>
       <c r="D2" t="n">
-        <v>67.5093</v>
+        <v>30.9824</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>22862.8285</v>
+        <v>729.8255</v>
       </c>
       <c r="D3" t="n">
-        <v>166.882</v>
+        <v>34.7536</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>68043.3958</v>
+        <v>1659.1484</v>
       </c>
       <c r="D4" t="n">
-        <v>358.1231</v>
+        <v>29.1079</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>2170.1921</v>
+        <v>1161.7859</v>
       </c>
       <c r="D5" t="n">
-        <v>72.33969999999999</v>
+        <v>25.8175</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>3379.1698</v>
+        <v>1054.6783</v>
       </c>
       <c r="D6" t="n">
-        <v>78.5853</v>
+        <v>29.2966</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>13349.3942</v>
+        <v>331.3919</v>
       </c>
       <c r="D7" t="n">
-        <v>158.9214</v>
+        <v>36.8213</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>4206.846</v>
+        <v>80.2132</v>
       </c>
       <c r="D8" t="n">
-        <v>85.854</v>
+        <v>40.1066</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>9978.6142</v>
+        <v>586.7178</v>
       </c>
       <c r="D9" t="n">
-        <v>169.1291</v>
+        <v>48.8932</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>1155.862</v>
+        <v>567.529</v>
       </c>
       <c r="D10" t="n">
-        <v>41.2808</v>
+        <v>37.8353</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>34426.5906</v>
+        <v>34.2426</v>
       </c>
       <c r="D11" t="n">
-        <v>277.6338</v>
+        <v>34.2426</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>

--- a/results/canaliculi/543_3/measurements.xlsx
+++ b/results/canaliculi/543_3/measurements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="per_lacuna" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_lacuna" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,13 +531,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.7778</v>
+        <v>47.1111</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>18.2536</v>
+        <v>28.7943</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -554,13 +555,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>744.2212</v>
+        <v>1435.1469</v>
       </c>
       <c r="C8" t="n">
-        <v>586.7178</v>
+        <v>1516.2367</v>
       </c>
       <c r="D8" t="n">
-        <v>477.3259</v>
+        <v>827.0078999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -578,13 +579,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.846</v>
+        <v>30.6592</v>
       </c>
       <c r="C9" t="n">
-        <v>34.7536</v>
+        <v>28.9741</v>
       </c>
       <c r="D9" t="n">
-        <v>7.0534</v>
+        <v>4.7005</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -606,6 +607,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>per-field metrics -- independent of the per-lacuna assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only ~23% of skeleton length is graph-connected to any lacuna in these 2D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sections, so per-cell numbers use a quarter of the network. These use all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analysed_area_px2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1028360</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_skeleton_length_px</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>46420</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_per_px</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.04513983</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>junction_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>698</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junction_density_per_px2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00067875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lacuna_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lacunae_per_px2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9.72e-06</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeleton_component_count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>711</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mean_component_length_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>65.28830000000001</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>median_component_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>14</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -646,13 +847,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>526.7006</v>
+        <v>724.3524</v>
       </c>
       <c r="D2" t="n">
-        <v>30.9824</v>
+        <v>28.9741</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -668,13 +869,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>729.8255</v>
+        <v>1420.8103</v>
       </c>
       <c r="D3" t="n">
-        <v>34.7536</v>
+        <v>28.4162</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -690,13 +891,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>1659.1484</v>
+        <v>2529.8856</v>
       </c>
       <c r="D4" t="n">
-        <v>29.1079</v>
+        <v>31.6236</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -712,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="C5" t="n">
-        <v>1161.7859</v>
+        <v>2573.6846</v>
       </c>
       <c r="D5" t="n">
-        <v>25.8175</v>
+        <v>27.3796</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -734,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>1054.6783</v>
+        <v>1754.8885</v>
       </c>
       <c r="D6" t="n">
-        <v>29.2966</v>
+        <v>30.7875</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -756,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>331.3919</v>
+        <v>1516.2367</v>
       </c>
       <c r="D7" t="n">
-        <v>36.8213</v>
+        <v>28.6082</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -778,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>80.2132</v>
+        <v>96.3553</v>
       </c>
       <c r="D8" t="n">
-        <v>40.1066</v>
+        <v>24.0888</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -800,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>586.7178</v>
+        <v>1601.526</v>
       </c>
       <c r="D9" t="n">
-        <v>48.8932</v>
+        <v>37.2448</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -822,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>567.529</v>
+        <v>698.5828</v>
       </c>
       <c r="D10" t="n">
-        <v>37.8353</v>
+        <v>38.8102</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -847,10 +1048,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>34.2426</v>
+        <v>43.2426</v>
       </c>
       <c r="D11" t="n">
-        <v>34.2426</v>
+        <v>43.2426</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
